--- a/sampleprojects/CorporateTax/excel/states/ID_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/ID_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus or doing business threshold; result.id_gross_receipts is greater than or equal to result.id_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.id_gross_receipts &gt;= result.id_economic_nexus_threshold</t>
+    <t>id_result.gross_receipts &gt;= id_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.id_has_nexus = true;</t>
+    <t>set id_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.id_has_nexus = false; set result.id_tax_liability = 0.0;</t>
+    <t>set id_result.has_nexus = false; set id_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate ID Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Idaho nexus</t>
   </si>
   <si>
-    <t>result.id_has_nexus is equal to true</t>
+    <t>id_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Idaho state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.id_state_additions = 0.0; if result.id_state_taxes_deducted != 0.0 then set result.id_state_additions = result.id_state_additions + result.id_state_taxes_deducted; endif set result.id_state_subtractions = 0.0; if result.id_us_interest_income != 0.0 then set result.id_state_subtractions = result.id_state_subtractions + result.id_us_interest_income; endif if result.id_municipal_interest != 0.0 then set result.id_state_subtractions = result.id_state_subtractions + result.id_municipal_interest; endif add (("Idaho additions: $" + string value of (result.id_state_additions)) + ", subtractions: $") + string value of (result.id_state_subtractions) to job.audit_trail;</t>
+    <t>set id_result.state_additions = 0.0; if id_result.state_taxes_deducted != 0.0 then set id_result.state_additions = id_result.state_additions + id_result.state_taxes_deducted; endif set id_result.state_subtractions = 0.0; if id_result.us_interest_income != 0.0 then set id_result.state_subtractions = id_result.state_subtractions + id_result.us_interest_income; endif if id_result.municipal_interest != 0.0 then set id_result.state_subtractions = id_result.state_subtractions + id_result.municipal_interest; endif add (("Idaho additions: $" + string value of (id_result.state_additions)) + ", subtractions: $") + string value of (id_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.id_state_additions = 0.0; set result.id_state_subtractions = 0.0;</t>
+    <t>set id_result.state_additions = 0.0; set id_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate ID State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.id_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.id_apportioned_income &gt; 0.0</t>
+    <t>id_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Idaho corporate tax (flat rate 5.3%); Apply Idaho 5.3% flat rate</t>
   </si>
   <si>
-    <t>set result.id_taxable_income = the maximum of (result.id_apportioned_income + result.id_state_additions - result.id_state_subtractions) and (0.0); set result.id_tax_liability = the maximum of (result.id_taxable_income * result.id_corp_tax_rate - result.id_state_credits) and (0.0); set result.id_refund_or_owed = result.id_estimated_payments - result.id_tax_liability; add "Idaho taxable income: $" + string value of (result.id_taxable_income) to job.audit_trail; add "Idaho tax liability (5.3%): $" + string value of (result.id_tax_liability) to job.audit_trail;</t>
+    <t>set id_result.taxable_income = the maximum of (id_result.apportioned_income + id_result.state_additions - id_result.state_subtractions) and (0.0); set id_result.tax_liability = the maximum of (id_result.taxable_income * id_result.corp_tax_rate - id_result.state_credits) and (0.0); set id_result.refund_or_owed = id_result.estimated_payments - id_result.tax_liability; add "Idaho taxable income: $" + string value of (id_result.taxable_income) to job.audit_trail; add "Idaho tax liability (5.3%): $" + string value of (id_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.id_taxable_income = 0.0; set result.id_tax_liability = 0.0;</t>
+    <t>set id_result.taxable_income = 0.0; set id_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,13 +205,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>id_result</t>
   </si>
   <si>
     <t>(17 attributes)</t>
   </si>
   <si>
-    <t>id_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -226,7 +226,7 @@
     <t>Declared from decision-table usage; referenced by ID but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>id_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -238,7 +238,7 @@
     <t>ID uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>id_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.053</t>
@@ -247,7 +247,7 @@
     <t>ID corporate income tax rate: 5.3% flat rate (effective 2025, Idaho Code § 63-3025)</t>
   </si>
   <si>
-    <t>id_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -256,13 +256,13 @@
     <t>ID economic nexus gross receipts threshold: $100,000 (primarily for sales tax)</t>
   </si>
   <si>
-    <t>id_estimated_payments</t>
-  </si>
-  <si>
-    <t>id_gross_receipts</t>
-  </si>
-  <si>
-    <t>id_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -274,46 +274,46 @@
     <t>Whether corporation has nexus with Idaho</t>
   </si>
   <si>
-    <t>id_municipal_interest</t>
-  </si>
-  <si>
-    <t>id_refund_or_owed</t>
-  </si>
-  <si>
-    <t>id_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>ID additions to federal taxable income (state income taxes deducted federally, certain expenses, etc.)</t>
   </si>
   <si>
-    <t>id_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>ID tax credits (investment tax credit, R&amp;D credit, broadband equipment credit, etc.)</t>
   </si>
   <si>
-    <t>id_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>ID subtractions from federal taxable income (U.S. government interest, Idaho municipal bond interest, state NOL, etc.)</t>
   </si>
   <si>
-    <t>id_state_taxes_deducted</t>
-  </si>
-  <si>
-    <t>id_tax_liability</t>
+    <t>state_taxes_deducted</t>
+  </si>
+  <si>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>ID corporate income tax liability</t>
   </si>
   <si>
-    <t>id_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>ID taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>id_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -325,7 +325,7 @@
     <t>ID does not use transaction count for corporate income tax nexus</t>
   </si>
   <si>
-    <t>id_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
